--- a/SuppXLS/Scen_B_TRA_F_ModalShares.xlsx
+++ b/SuppXLS/Scen_B_TRA_F_ModalShares.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olex\Documents\MANRID\ResLab\Modelling\TIMES\TIMES-IE\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\For_compare\tim-leaf v1.1\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B938705-B60D-4426-9E5B-A16260B45E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{117B8573-C0B6-49CB-8D16-217EAF615BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1350" yWindow="2040" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="16" r:id="rId1"/>
@@ -1292,9 +1292,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1332,9 +1332,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1367,26 +1367,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1419,26 +1402,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5551,7 +5517,7 @@
       </c>
       <c r="I13" s="23">
         <f>I$12/SUM(I$12,I$17,I$22)*(1-I$28)</f>
-        <v>2.5157895566592151E-2</v>
+        <v>2.5157514050693969E-2</v>
       </c>
       <c r="J13" s="23">
         <f t="shared" ref="J13:AI13" si="1">J$12/SUM(J$12,J$17,J$22)*(1-J$28)</f>
@@ -5677,7 +5643,7 @@
       </c>
       <c r="I14" s="23">
         <f>I$12/SUM(I$12,I$17,I$22)*(1-I$29)</f>
-        <v>2.5140541797434669E-2</v>
+        <v>2.5140114673733178E-2</v>
       </c>
       <c r="J14" s="23">
         <f t="shared" ref="J14:AI14" si="2">J$12/SUM(J$12,J$17,J$22)*(1-J$29)</f>
@@ -5803,7 +5769,7 @@
       </c>
       <c r="I15" s="23">
         <f>I$12/SUM(I$12,I$17,I$22)*(1-I$30)</f>
-        <v>2.5162481534476113E-2</v>
+        <v>2.5162112071055939E-2</v>
       </c>
       <c r="J15" s="23">
         <f t="shared" ref="J15:AI15" si="3">J$12/SUM(J$12,J$17,J$22)*(1-J$30)</f>
@@ -6103,7 +6069,7 @@
       </c>
       <c r="I18" s="23">
         <f>I$17/SUM(I$12,I$17,I$22)*(1-I$28)</f>
-        <v>9.8237023508735977E-2</v>
+        <v>9.8235533758285282E-2</v>
       </c>
       <c r="J18" s="23">
         <f t="shared" ref="J18:AI18" si="6">J$17/SUM(J$12,J$17,J$22)*(1-J$28)</f>
@@ -6230,7 +6196,7 @@
       </c>
       <c r="I19" s="23">
         <f>I$17/SUM(I$12,I$17,I$22)*(1-I$29)</f>
-        <v>9.8169260184725965E-2</v>
+        <v>9.816759234406762E-2</v>
       </c>
       <c r="J19" s="23">
         <f t="shared" ref="J19:AI19" si="7">J$17/SUM(J$12,J$17,J$22)*(1-J$29)</f>
@@ -6357,7 +6323,7 @@
       </c>
       <c r="I20" s="23">
         <f>I$17/SUM(I$12,I$17,I$22)*(1-I$30)</f>
-        <v>9.8254930882333044E-2</v>
+        <v>9.8253488194625052E-2</v>
       </c>
       <c r="J20" s="23">
         <f t="shared" ref="J20:AI20" si="8">J$17/SUM(J$12,J$17,J$22)*(1-J$30)</f>
@@ -6657,7 +6623,7 @@
       </c>
       <c r="I23" s="23">
         <f>I$22/SUM(I$12,I$17,I$22)*(1-I$28)</f>
-        <v>0.87086795720579713</v>
+        <v>0.87085475061743145</v>
       </c>
       <c r="J23" s="23">
         <f t="shared" ref="J23:AI23" si="11">J$22/SUM(J$12,J$17,J$22)*(1-J$28)</f>
@@ -6784,7 +6750,7 @@
       </c>
       <c r="I24" s="23">
         <f>I$22/SUM(I$12,I$17,I$22)*(1-I$29)</f>
-        <v>0.87026723758455549</v>
+        <v>0.870252452232402</v>
       </c>
       <c r="J24" s="23">
         <f t="shared" ref="J24:AI24" si="12">J$22/SUM(J$12,J$17,J$22)*(1-J$29)</f>
@@ -6911,7 +6877,7 @@
       </c>
       <c r="I25" s="23">
         <f>I$22/SUM(I$12,I$17,I$22)*(1-I$30)</f>
-        <v>0.87102670547917094</v>
+        <v>0.87101391610045931</v>
       </c>
       <c r="J25" s="23">
         <f t="shared" ref="J25:AI25" si="13">J$22/SUM(J$12,J$17,J$22)*(1-J$30)</f>
@@ -7080,11 +7046,11 @@
         <v>90</v>
       </c>
       <c r="I27" s="23">
-        <f t="shared" ref="I27:AI27" si="14">ROUNDDOWN(D48/D$49,5)</f>
-        <v>7.6099999999999996E-3</v>
+        <f>1-I12-I17-I22</f>
+        <v>7.6300000000000257E-3</v>
       </c>
       <c r="J27" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="I27:AI27" si="14">ROUNDDOWN(E48/E$49,5)</f>
         <v>0</v>
       </c>
       <c r="K27" s="23">
@@ -7209,7 +7175,7 @@
       </c>
       <c r="I28" s="23">
         <f>I$27*$C$54/$C$53/($D$48/SUM($D$45:$D$47))</f>
-        <v>5.7371237188748488E-3</v>
+        <v>5.7522015735893888E-3</v>
       </c>
       <c r="J28" s="23">
         <f t="shared" ref="J28:AI28" si="15">J$27*$C$54/$C$53/($D$48/SUM($D$45:$D$47))</f>
@@ -7335,7 +7301,7 @@
       </c>
       <c r="I29" s="23">
         <f>I$27*$D$54/$D$53/($D$48/SUM($D$45:$D$47))</f>
-        <v>6.4229604332839947E-3</v>
+        <v>6.4398407497972465E-3</v>
       </c>
       <c r="J29" s="23">
         <f t="shared" ref="J29:AI29" si="16">J$27*$D$54/$D$53/($D$48/SUM($D$45:$D$47))</f>
@@ -7461,7 +7427,7 @@
       </c>
       <c r="I30" s="23">
         <f>I$27*$E$54/$E$53/($D$48/SUM($D$45:$D$47))</f>
-        <v>5.555882104019921E-3</v>
+        <v>5.5704836338596776E-3</v>
       </c>
       <c r="J30" s="23">
         <f t="shared" ref="J30:AI30" si="17">J$27*$E$54/$E$53/($D$48/SUM($D$45:$D$47))</f>
@@ -7620,11 +7586,11 @@
         <v>72</v>
       </c>
       <c r="I33" s="25">
-        <f t="shared" ref="I33:AI33" si="18">I12+I17+I22+I27</f>
-        <v>0.99997999999999998</v>
+        <f>I12+I17+I22+I27</f>
+        <v>1</v>
       </c>
       <c r="J33" s="25">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="I33:AI33" si="18">J12+J17+J22+J27</f>
         <v>0.99997999999999998</v>
       </c>
       <c r="K33" s="15">
